--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484050_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484050_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4445</v>
+        <v>10.0222</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1828</v>
+        <v>8.041</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2617</v>
+        <v>1.9812</v>
       </c>
       <c r="G2" t="n">
         <v>8.6486</v>
@@ -610,13 +610,13 @@
         <v>3.1741</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.3655</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2778</v>
+        <v>0.1361</v>
       </c>
       <c r="U2" t="n">
-        <v>0.51</v>
+        <v>0.2294</v>
       </c>
       <c r="V2" t="n">
         <v>1.2065</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.802899999999999</v>
+        <v>9.7902</v>
       </c>
       <c r="E3" t="n">
-        <v>9.2538</v>
+        <v>9.661899999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5491</v>
+        <v>0.1283</v>
       </c>
       <c r="G3" t="n">
         <v>8.9269</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6262</v>
+        <v>0.6135</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.102</v>
+        <v>0.3061</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7282</v>
+        <v>0.3073</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9405</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.675</v>
+        <v>5.791</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2676</v>
+        <v>3.4117</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4074</v>
+        <v>2.3793</v>
       </c>
       <c r="G4" t="n">
         <v>1.0054</v>
@@ -766,13 +766,13 @@
         <v>3.3725</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6534</v>
+        <v>0.7694</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4512</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2022</v>
+        <v>0.1742</v>
       </c>
       <c r="V4" t="n">
         <v>3.6194</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9211</v>
+        <v>5.0574</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5308</v>
+        <v>3.6952</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3903</v>
+        <v>1.3623</v>
       </c>
       <c r="G5" t="n">
         <v>4.3059</v>
@@ -844,13 +844,13 @@
         <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5119</v>
+        <v>-0.3755</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4251</v>
+        <v>-0.2607</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0868</v>
+        <v>-0.1149</v>
       </c>
       <c r="V5" t="n">
         <v>0.532</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3932</v>
+        <v>3.3739</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9252</v>
+        <v>1.6815</v>
       </c>
       <c r="F6" t="n">
-        <v>1.468</v>
+        <v>1.6924</v>
       </c>
       <c r="G6" t="n">
         <v>2.2747</v>
@@ -922,13 +922,13 @@
         <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3378</v>
+        <v>-0.3571</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1304</v>
+        <v>-0.1133</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4682</v>
+        <v>-0.2438</v>
       </c>
       <c r="V6" t="n">
         <v>0.266</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5364</v>
+        <v>2.1409</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0304</v>
+        <v>1.4385</v>
       </c>
       <c r="F7" t="n">
-        <v>0.506</v>
+        <v>0.7023</v>
       </c>
       <c r="G7" t="n">
         <v>1.1419</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3395</v>
+        <v>0.265</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3004</v>
+        <v>0.1077</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0392</v>
+        <v>0.1572</v>
       </c>
       <c r="V7" t="n">
         <v>0.3373</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1476</v>
+        <v>1.3604</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8904</v>
+        <v>1.8507</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7429</v>
+        <v>-0.4904</v>
       </c>
       <c r="G8" t="n">
         <v>0.9302</v>
@@ -1078,13 +1078,13 @@
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1037</v>
+        <v>0.1091</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3798</v>
+        <v>0.3401</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4836</v>
+        <v>-0.2311</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8692</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.9008</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0725</v>
+        <v>1.3786</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3936</v>
+        <v>-0.4778</v>
       </c>
       <c r="G9" t="n">
         <v>1.4475</v>
@@ -1156,13 +1156,13 @@
         <v>2.3806</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7363</v>
+        <v>-0.5144</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5498</v>
+        <v>-0.2437</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1865</v>
+        <v>-0.2707</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4129</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2064</v>
+        <v>-0.0483</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1054</v>
+        <v>-0.0033</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.101</v>
+        <v>-0.0449</v>
       </c>
       <c r="G10" t="n">
         <v>0.6801</v>
@@ -1234,13 +1234,13 @@
         <v>0.1984</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3707</v>
+        <v>-0.2126</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3084</v>
+        <v>-0.2523</v>
       </c>
       <c r="V10" t="n">
         <v>0.6745</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0078</v>
+        <v>-0.6176</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3198</v>
+        <v>-0.0138</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.6038</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4801</v>
@@ -1312,13 +1312,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1309</v>
+        <v>0.2593</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.051</v>
+        <v>0.2551</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0799</v>
+        <v>0.0042</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7082</v>
+        <v>-2.0704</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0927</v>
+        <v>-0.3988</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6155</v>
+        <v>-1.6716</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3283</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0249</v>
+        <v>-0.3373</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4308</v>
+        <v>0.1247</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4059</v>
+        <v>-0.462</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2065</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.758</v>
+        <v>-2.4698</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2522</v>
+        <v>-0.0482</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5058</v>
+        <v>-2.4216</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6781</v>
@@ -1468,13 +1468,13 @@
         <v>0.5952</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4767</v>
+        <v>-0.1885</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0113</v>
+        <v>0.2154</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.488</v>
+        <v>-0.4039</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2065</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.91919999999999</v>
+        <v>33.23070000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>30.3834</v>
+        <v>30.695</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5357</v>
+        <v>2.535700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>27.8747</v>
@@ -1546,13 +1546,13 @@
         <v>19.8384</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08479999999999976</v>
+        <v>0.3964</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1907</v>
+        <v>1.5025</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1061</v>
+        <v>-1.1064</v>
       </c>
       <c r="V14" t="n">
         <v>0.0001000000000010992</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2911</v>
+        <v>3.6032</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7826</v>
+        <v>2.9867</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5085</v>
+        <v>0.6165</v>
       </c>
       <c r="G15" t="n">
         <v>1.8427</v>
@@ -1624,13 +1624,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4404</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1418</v>
+        <v>0.3458</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2986</v>
+        <v>0.4066</v>
       </c>
       <c r="V15" t="n">
         <v>1.2065</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6022999999999999</v>
+        <v>1.206</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1767</v>
+        <v>3.7889</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5744</v>
+        <v>-2.5828</v>
       </c>
       <c r="G16" t="n">
         <v>-3.7563</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6575</v>
+        <v>-0.0538</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0995</v>
+        <v>-0.4873</v>
       </c>
       <c r="U16" t="n">
-        <v>0.442</v>
+        <v>0.4335</v>
       </c>
       <c r="V16" t="n">
         <v>4.2226</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2555</v>
+        <v>-1.3733</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8704</v>
+        <v>-0.7914</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1258</v>
+        <v>-0.5819</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1879</v>
+        <v>-2.112</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4939</v>
+        <v>0.3729</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.6818</v>
+        <v>-2.4849</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7513</v>
+        <v>0.3535</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4315</v>
+        <v>1.1089</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6802</v>
+        <v>-0.7554</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9392</v>
+        <v>-2.4655</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9376</v>
+        <v>-0.736</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0016</v>
+        <v>-1.7295</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9324</v>
+        <v>0.1318</v>
       </c>
       <c r="T17" t="n">
-        <v>1.111</v>
+        <v>-0.153</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1786</v>
+        <v>0.2848</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0322</v>
+        <v>-1.7274</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8465</v>
+        <v>0.2582</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1857</v>
+        <v>-1.9856</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5063</v>
+        <v>-2.1879</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2472</v>
+        <v>0.4939</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2591</v>
+        <v>-2.6818</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0806</v>
+        <v>0.7513</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0806</v>
+        <v>1.4315</v>
       </c>
       <c r="L18" t="n">
+        <v>-0.6802</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-2.9392</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.9376</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.0016</v>
+      </c>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>-0.587</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.3279</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.2591</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-2.579</v>
-      </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0531</v>
+        <v>0.4606</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0487</v>
+        <v>0.4988</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0045</v>
+        <v>-0.0383</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0816</v>
+        <v>-2.9606</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1996</v>
+        <v>-2.6627</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.882</v>
+        <v>-0.2979</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.112</v>
+        <v>-0.5063</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3729</v>
+        <v>-0.2472</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4849</v>
+        <v>-0.2591</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3535</v>
+        <v>0.0806</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1089</v>
+        <v>0.0806</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7554</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4655</v>
+        <v>-0.587</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.736</v>
+        <v>-0.3279</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7295</v>
+        <v>-0.2591</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1984</v>
+        <v>-2.579</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5764</v>
+        <v>0.1247</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5611</v>
+        <v>0.2324</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0153</v>
+        <v>-0.1077</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4085</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4887</v>
+        <v>-3.0006</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.457</v>
+        <v>-1.0489</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0317</v>
+        <v>-1.9517</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1427</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0601</v>
+        <v>0.4279</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.102</v>
+        <v>0.3061</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0419</v>
+        <v>0.1218</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4842</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7267</v>
+        <v>-3.1281</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3012</v>
+        <v>-0.1992</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4255</v>
+        <v>-2.929</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1541</v>
@@ -2092,13 +2092,13 @@
         <v>2.3806</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.3627</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.357</v>
+        <v>-0.2549</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.1077</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2729</v>
+        <v>-4.4865</v>
       </c>
       <c r="E22" t="n">
-        <v>1.926</v>
+        <v>-3.6787</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.1989</v>
+        <v>-0.8078</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5404</v>
+        <v>-2.5754</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2178</v>
+        <v>-1.9147</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7581</v>
+        <v>-0.6607</v>
       </c>
       <c r="J22" t="n">
-        <v>4.1987</v>
+        <v>-1.3148</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1586</v>
+        <v>-1.3148</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.7391</v>
+        <v>-1.2607</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9408</v>
+        <v>-0.6</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.7983</v>
+        <v>-0.6607</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5452</v>
+        <v>0.5371</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3775</v>
+        <v>0.3458</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1677</v>
+        <v>0.1913</v>
       </c>
       <c r="V22" t="n">
-        <v>-4.2939</v>
+        <v>-0.266</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.6194</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3291</v>
+        <v>-6.0075</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1889</v>
+        <v>1.0077</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1402</v>
+        <v>-7.0152</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5754</v>
+        <v>-0.5404</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9147</v>
+        <v>2.2178</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6607</v>
+        <v>-2.7581</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3148</v>
+        <v>4.1987</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3148</v>
+        <v>4.1586</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2607</v>
+        <v>-4.7391</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6</v>
+        <v>-1.9408</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6607</v>
+        <v>-2.7983</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3055</v>
+        <v>0.8106</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1643</v>
+        <v>0.4592</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1412</v>
+        <v>0.3514</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.266</v>
+        <v>-4.2939</v>
       </c>
       <c r="W23" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.532</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4092</v>
+        <v>-6.2349</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0535</v>
+        <v>-0.1555</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.3557</v>
+        <v>-6.0794</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9671</v>
@@ -2326,13 +2326,13 @@
         <v>1.5871</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7793</v>
+        <v>-0.605</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0566</v>
+        <v>-0.1586</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7227</v>
+        <v>-0.4464</v>
       </c>
       <c r="V24" t="n">
         <v>-0.266</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2167</v>
+        <v>-6.7686</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2447</v>
+        <v>-2.0407</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.972</v>
+        <v>-4.728</v>
       </c>
       <c r="G25" t="n">
         <v>-7.7749</v>
@@ -2404,13 +2404,13 @@
         <v>1.7855</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7158</v>
+        <v>-0.2678</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2323</v>
+        <v>-0.0282</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4836</v>
+        <v>-0.2395</v>
       </c>
       <c r="V25" t="n">
         <v>1.4724</v>
@@ -2437,31 +2437,31 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.9192</v>
+        <v>-30.8783</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5357</v>
+        <v>-2.5356</v>
       </c>
       <c r="F26" t="n">
-        <v>-30.3834</v>
+        <v>-28.3428</v>
       </c>
       <c r="G26" t="n">
         <v>-27.8744</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3766000000000003</v>
+        <v>-0.3766000000000007</v>
       </c>
       <c r="I26" t="n">
         <v>-27.4978</v>
       </c>
       <c r="J26" t="n">
-        <v>8.107600000000001</v>
+        <v>8.1076</v>
       </c>
       <c r="K26" t="n">
         <v>15.6548</v>
       </c>
       <c r="L26" t="n">
-        <v>-7.547099999999999</v>
+        <v>-7.5471</v>
       </c>
       <c r="M26" t="n">
         <v>-35.9824</v>
@@ -2482,16 +2482,16 @@
         <v>14.8789</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.08469999999999989</v>
+        <v>1.9559</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1062</v>
+        <v>1.1061</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.191</v>
+        <v>0.8497999999999997</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="W26" t="n">
         <v>8.088900000000001</v>
